--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="199">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-07T13:22:03+00:00</t>
+    <t>2024-06-18T08:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -312,6 +312,9 @@
     <t>Reason for the status</t>
   </si>
   <si>
+    <t xml:space="preserve"> We consider this is not necessary - should we add?</t>
+  </si>
+  <si>
     <t>be-model-medicationline.assertedDate</t>
   </si>
   <si>
@@ -558,7 +561,7 @@
     <t>be-model-medicationline.adherence.modifierExtension</t>
   </si>
   <si>
-    <t>be-model-medicationline.adherence.status</t>
+    <t>be-model-medicationline.adherence.code</t>
   </si>
   <si>
     <t>The status - taking, not taking,...</t>
@@ -1300,7 +1303,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>80</v>
@@ -1375,7 +1378,7 @@
         <v>84</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH4" t="s" s="2">
         <v>80</v>
@@ -1625,7 +1628,9 @@
       <c r="M7" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="N7" s="2"/>
+      <c r="N7" t="s" s="2">
+        <v>97</v>
+      </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
         <v>74</v>
@@ -1691,10 +1696,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1720,13 +1725,13 @@
         <v>88</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1776,7 +1781,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>75</v>
@@ -1793,10 +1798,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1819,16 +1824,16 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1878,7 +1883,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1895,10 +1900,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1921,13 +1926,13 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1978,7 +1983,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1995,10 +2000,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2009,7 +2014,7 @@
         <v>75</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>74</v>
@@ -2021,13 +2026,13 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2078,27 +2083,27 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2124,10 +2129,10 @@
         <v>85</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2178,7 +2183,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
@@ -2195,14 +2200,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2221,16 +2226,16 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2268,19 +2273,19 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2292,19 +2297,19 @@
         <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2317,25 +2322,25 @@
         <v>74</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>74</v>
@@ -2384,7 +2389,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>75</v>
@@ -2396,15 +2401,15 @@
         <v>74</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2430,10 +2435,10 @@
         <v>95</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2484,7 +2489,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
@@ -2501,10 +2506,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2527,13 +2532,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2584,7 +2589,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2596,15 +2601,15 @@
         <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2630,10 +2635,10 @@
         <v>85</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2684,7 +2689,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>75</v>
@@ -2701,14 +2706,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -2727,16 +2732,16 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2774,19 +2779,19 @@
         <v>74</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>75</v>
@@ -2798,19 +2803,19 @@
         <v>74</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -2823,25 +2828,25 @@
         <v>74</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>74</v>
@@ -2890,7 +2895,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
@@ -2902,15 +2907,15 @@
         <v>74</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2933,13 +2938,13 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2990,7 +2995,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3007,10 +3012,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3036,10 +3041,10 @@
         <v>95</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3066,11 +3071,11 @@
         <v>74</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>74</v>
@@ -3088,7 +3093,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3105,10 +3110,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3134,10 +3139,10 @@
         <v>95</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3164,11 +3169,11 @@
         <v>74</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Y22" s="2"/>
       <c r="Z22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>74</v>
@@ -3186,7 +3191,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3203,10 +3208,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3229,13 +3234,13 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3286,7 +3291,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3298,15 +3303,15 @@
         <v>74</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3332,10 +3337,10 @@
         <v>85</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3386,7 +3391,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>75</v>
@@ -3403,14 +3408,14 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -3429,16 +3434,16 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -3476,19 +3481,19 @@
         <v>74</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3500,19 +3505,19 @@
         <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -3525,25 +3530,25 @@
         <v>74</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>74</v>
@@ -3592,7 +3597,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
@@ -3604,15 +3609,15 @@
         <v>74</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3635,13 +3640,13 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3692,7 +3697,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>75</v>
@@ -3709,10 +3714,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3738,10 +3743,10 @@
         <v>95</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3792,7 +3797,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3809,10 +3814,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3835,16 +3840,16 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3894,7 +3899,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3906,15 +3911,15 @@
         <v>74</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3940,10 +3945,10 @@
         <v>85</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3994,7 +3999,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>75</v>
@@ -4011,14 +4016,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4037,16 +4042,16 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4084,19 +4089,19 @@
         <v>74</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
@@ -4108,19 +4113,19 @@
         <v>74</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4133,25 +4138,25 @@
         <v>74</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>74</v>
@@ -4200,7 +4205,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>75</v>
@@ -4212,15 +4217,15 @@
         <v>74</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4246,10 +4251,10 @@
         <v>88</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4300,7 +4305,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4317,10 +4322,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4346,10 +4351,10 @@
         <v>88</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4400,7 +4405,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
@@ -4417,10 +4422,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4443,13 +4448,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4500,7 +4505,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
@@ -4512,15 +4517,15 @@
         <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4546,10 +4551,10 @@
         <v>85</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4600,7 +4605,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>75</v>
@@ -4617,14 +4622,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -4643,16 +4648,16 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -4690,19 +4695,19 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>
@@ -4714,19 +4719,19 @@
         <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -4739,25 +4744,25 @@
         <v>74</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>74</v>
@@ -4806,7 +4811,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -4818,15 +4823,15 @@
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4852,10 +4857,10 @@
         <v>95</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4906,7 +4911,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -4923,10 +4928,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4952,10 +4957,10 @@
         <v>95</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5006,7 +5011,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5023,10 +5028,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5049,13 +5054,13 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5106,7 +5111,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>75</v>
@@ -5118,15 +5123,15 @@
         <v>74</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5152,10 +5157,10 @@
         <v>85</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5206,7 +5211,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>75</v>
@@ -5223,14 +5228,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -5249,16 +5254,16 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -5296,19 +5301,19 @@
         <v>74</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>75</v>
@@ -5320,19 +5325,19 @@
         <v>74</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -5345,25 +5350,25 @@
         <v>74</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>74</v>
@@ -5412,7 +5417,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>75</v>
@@ -5424,15 +5429,15 @@
         <v>74</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -5455,13 +5460,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5512,7 +5517,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>75</v>
@@ -5529,10 +5534,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5555,16 +5560,16 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -5614,7 +5619,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>75</v>
@@ -5631,10 +5636,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -5642,7 +5647,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>80</v>
@@ -5660,12 +5665,14 @@
         <v>95</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>191</v>
+      </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>74</v>
@@ -5714,10 +5721,10 @@
         <v>74</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>80</v>
@@ -5731,10 +5738,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -5757,13 +5764,13 @@
         <v>74</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -5814,7 +5821,7 @@
         <v>74</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>75</v>
@@ -5831,10 +5838,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -5845,7 +5852,7 @@
         <v>75</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>74</v>
@@ -5860,10 +5867,10 @@
         <v>95</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -5914,13 +5921,13 @@
         <v>74</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>74</v>

--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T08:46:48+00:00</t>
+    <t>2024-06-18T10:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,6 +631,12 @@
   </si>
   <si>
     <t>Whether the medication needs a prescription or request to be dispensed</t>
+  </si>
+  <si>
+    <t>be-model-medicationline.visibility</t>
+  </si>
+  <si>
+    <t>Whether the patient has explicitly requested the medication line not to be seen - when other rules don't prevail</t>
   </si>
 </sst>
 </file>
@@ -940,7 +946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AJ50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.46875" customWidth="true" bestFit="true"/>
@@ -5936,6 +5942,106 @@
         <v>74</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:21+00:00</t>
+    <t>2024-06-18T10:57:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:57:59+00:00</t>
+    <t>2024-06-18T10:58:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T10:58:59+00:00</t>
+    <t>2024-06-18T11:16:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-18T11:16:13+00:00</t>
+    <t>2024-07-02T10:09:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>HL7 Belgium (https://www.hl7belgium.org, hl7belgium@hl7belgium.org)</t>
   </si>
   <si>
-    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(WORK))</t>
+    <t>Message Structure eHealth (message-structure@ehealth.fgov.be(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="199">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-02T10:09:21+00:00</t>
+    <t>2024-09-06T15:59:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,12 +631,6 @@
   </si>
   <si>
     <t>Whether the medication needs a prescription or request to be dispensed</t>
-  </si>
-  <si>
-    <t>be-model-medicationline.visibility</t>
-  </si>
-  <si>
-    <t>Whether the patient has explicitly requested the medication line not to be seen - when other rules don't prevail</t>
   </si>
 </sst>
 </file>
@@ -946,7 +940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ50"/>
+  <dimension ref="A1:AJ49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.46875" customWidth="true" bestFit="true"/>
@@ -5942,106 +5936,6 @@
         <v>74</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1586" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="201">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T15:59:56+00:00</t>
+    <t>2024-09-06T16:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -631,6 +631,12 @@
   </si>
   <si>
     <t>Whether the medication needs a prescription or request to be dispensed</t>
+  </si>
+  <si>
+    <t>be-model-medicationline.visibility</t>
+  </si>
+  <si>
+    <t>Whether the patient has explicitly requested the medication line not to be seen - when other rules don't prevail</t>
   </si>
 </sst>
 </file>
@@ -940,7 +946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ49"/>
+  <dimension ref="A1:AJ50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.46875" customWidth="true" bestFit="true"/>
@@ -5936,6 +5942,106 @@
         <v>74</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>200</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/StructureDefinition-be-model-medicationline.xlsx
+++ b/StructureDefinition-be-model-medicationline.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T16:05:52+00:00</t>
+    <t>2024-10-22T10:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
